--- a/reports/evaluation/ranker_training_report.xlsx
+++ b/reports/evaluation/ranker_training_report.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
   <si>
     <t>model_type</t>
   </si>
@@ -28,19 +28,28 @@
     <t>feature_count</t>
   </si>
   <si>
+    <t>cv_folds</t>
+  </si>
+  <si>
     <t>mae_in_sample</t>
   </si>
   <si>
     <t>r2_in_sample</t>
   </si>
   <si>
+    <t>mae_cv</t>
+  </si>
+  <si>
+    <t>r2_cv</t>
+  </si>
+  <si>
     <t>note</t>
   </si>
   <si>
     <t>gradient_boosting</t>
   </si>
   <si>
-    <t>MVP용 소규모 데이터의 in-sample 결과입니다. 생산 모델 성능으로 과장하지 않고 암묵지 학습 실증 개념으로 해석해야 합니다.</t>
+    <t>MVP용 소규모 데이터 결과입니다. 생산 모델 성능으로 과장하지 않고 암묵지 학습 실증 개념으로 해석해야 합니다. 5-fold 교차검증 out-of-sample 지표(mae_cv/r2_cv)를 함께 산출했습니다. 일반화 성능은 in-sample이 아닌 CV 기준으로 해석해야 합니다.</t>
   </si>
   <si>
     <t>scenario_name</t>
@@ -584,10 +593,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,10 +615,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -618,13 +636,22 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>0.03813040597024724</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>0.9999935985735532</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>0.1253918292906548</v>
+      </c>
+      <c r="F2">
+        <v>0.9999404337602056</v>
+      </c>
+      <c r="G2">
+        <v>12.66241048217999</v>
+      </c>
+      <c r="H2">
+        <v>-0.4119562226948621</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -639,50 +666,50 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2">
-        <v>0.9980205641095037</v>
+        <v>0.9974474371572508</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -691,30 +718,30 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>0.9935368070037682</v>
+        <v>0.9974474371572508</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -729,66 +756,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -806,13 +833,13 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>82.57122999999999</v>
+        <v>83.85393999999999</v>
       </c>
       <c r="J2">
-        <v>92.12506713759549</v>
+        <v>92.08215433577567</v>
       </c>
       <c r="K2">
-        <v>0.6681571428571429</v>
+        <v>0.6684142857142857</v>
       </c>
       <c r="L2">
         <v>92.202</v>
@@ -835,43 +862,43 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>76.09411999999999</v>
+        <v>75.5758</v>
       </c>
       <c r="J3">
-        <v>50.03060684747887</v>
+        <v>48.85282295672324</v>
       </c>
       <c r="K3">
-        <v>0.2212852953210594</v>
+        <v>0.1179641005309339</v>
       </c>
       <c r="L3">
-        <v>50.049</v>
+        <v>49.02</v>
       </c>
       <c r="M3">
-        <v>38.235</v>
+        <v>35.294</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -888,46 +915,46 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>75.14403999999999</v>
+        <v>75.72197</v>
       </c>
       <c r="J4">
-        <v>46.96644294363724</v>
+        <v>48.04866295692377</v>
       </c>
       <c r="K4">
-        <v>0.06889635435837743</v>
+        <v>0.1724980856091174</v>
       </c>
       <c r="L4">
-        <v>46.961</v>
+        <v>47.854</v>
       </c>
       <c r="M4">
         <v>29.412</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="O4">
         <v>83.333</v>
@@ -941,37 +968,37 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
-        <v>75.71343999999999</v>
+        <v>75.23186</v>
       </c>
       <c r="J5">
-        <v>46.85639184001016</v>
+        <v>46.94281661630287</v>
       </c>
       <c r="K5">
-        <v>0.1646994769048391</v>
+        <v>0.05754202607881254</v>
       </c>
       <c r="L5">
         <v>46.824</v>
@@ -994,19 +1021,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1018,22 +1045,22 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>76.05423999999999</v>
+        <v>76.50287</v>
       </c>
       <c r="J6">
-        <v>43.7934912312782</v>
+        <v>46.66154313427446</v>
       </c>
       <c r="K6">
-        <v>0.2519774753419622</v>
+        <v>0.2947616366154081</v>
       </c>
       <c r="L6">
-        <v>43.736</v>
+        <v>46.688</v>
       </c>
       <c r="M6">
-        <v>17.647</v>
+        <v>23.529</v>
       </c>
       <c r="N6">
-        <v>3.571</v>
+        <v>7.143</v>
       </c>
       <c r="O6">
         <v>83.333</v>
@@ -1057,92 +1084,92 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>0.05</v>
       </c>
       <c r="C2">
-        <v>0.2975817440753323</v>
+        <v>0.2976881088847934</v>
       </c>
       <c r="D2">
-        <v>0.1861699592414328</v>
+        <v>0.1862284598866364</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>0.05</v>
       </c>
       <c r="C3">
-        <v>0.2962545024393946</v>
+        <v>0.2969153065494276</v>
       </c>
       <c r="D3">
-        <v>0.185439976341667</v>
+        <v>0.1858034186021852</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>0.07000000000000001</v>
       </c>
       <c r="C4">
-        <v>0.2584563960247734</v>
+        <v>0.2422405782993529</v>
       </c>
       <c r="D4">
-        <v>0.1736510178136254</v>
+        <v>0.1647323180646442</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>0.09</v>
       </c>
       <c r="C5">
-        <v>0.1477073574604995</v>
+        <v>0.1631560062664259</v>
       </c>
       <c r="D5">
-        <v>0.1217390466032748</v>
+        <v>0.1302358034465343</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>0.22</v>
@@ -1151,15 +1178,15 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.09899999999999999</v>
+        <v>0.09900000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>0.16</v>
@@ -1168,15 +1195,15 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.07199999999999999</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8">
         <v>0.09</v>
@@ -1185,15 +1212,15 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.04049999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>0.09</v>
@@ -1202,15 +1229,15 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.04049999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>0.08</v>
@@ -1222,12 +1249,12 @@
         <v>0.036</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>0.06</v>
@@ -1239,12 +1266,12 @@
         <v>0.027</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>0.03</v>
@@ -1256,12 +1283,12 @@
         <v>0.0135</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>0.01</v>
@@ -1270,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0.0045</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
